--- a/artfynd/A 37076-2021 artfynd.xlsx
+++ b/artfynd/A 37076-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37076-2021 artfynd.xlsx
+++ b/artfynd/A 37076-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>77236432</v>
+        <v>77236431</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>605980.5526313845</v>
+        <v>605923</v>
       </c>
       <c r="R2" t="n">
-        <v>6657556.104001246</v>
+        <v>6657619</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2019-04-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-04-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>77236433</v>
+        <v>77236432</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605905.2663871016</v>
+        <v>605981</v>
       </c>
       <c r="R3" t="n">
-        <v>6657649.411479429</v>
+        <v>6657556</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +845,9 @@
           <t>2019-04-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-04-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>77236431</v>
+        <v>77236433</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>605922.6520303488</v>
+        <v>605905</v>
       </c>
       <c r="R4" t="n">
-        <v>6657619.420279783</v>
+        <v>6657649</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +947,9 @@
           <t>2019-04-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-04-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
